--- a/artfynd/A 49831-2025 artfynd.xlsx
+++ b/artfynd/A 49831-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129687266</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>57729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129687267</v>
       </c>
       <c r="B3" t="n">
-        <v>57889</v>
+        <v>57893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129685099</v>
       </c>
       <c r="B4" t="n">
-        <v>57889</v>
+        <v>57893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,27 +1020,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129685100</v>
+        <v>129685320</v>
       </c>
       <c r="B5" t="n">
-        <v>58101</v>
+        <v>57732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459097</v>
+        <v>459041</v>
       </c>
       <c r="R5" t="n">
         <v>6229261</v>
       </c>
       <c r="S5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,27 +1135,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129685320</v>
+        <v>129685100</v>
       </c>
       <c r="B6" t="n">
-        <v>57728</v>
+        <v>58105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1178,13 +1178,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459041</v>
+        <v>459097</v>
       </c>
       <c r="R6" t="n">
         <v>6229261</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,7 +1253,7 @@
         <v>129685322</v>
       </c>
       <c r="B7" t="n">
-        <v>57889</v>
+        <v>57893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>129683182</v>
       </c>
       <c r="B8" t="n">
-        <v>57889</v>
+        <v>57893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129686779</v>
       </c>
       <c r="B9" t="n">
-        <v>57889</v>
+        <v>57893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49831-2025 artfynd.xlsx
+++ b/artfynd/A 49831-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129687266</v>
       </c>
       <c r="B2" t="n">
-        <v>57729</v>
+        <v>57730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129687267</v>
       </c>
       <c r="B3" t="n">
-        <v>57893</v>
+        <v>57894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129685099</v>
       </c>
       <c r="B4" t="n">
-        <v>57893</v>
+        <v>57894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129685320</v>
       </c>
       <c r="B5" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129685100</v>
       </c>
       <c r="B6" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129685322</v>
       </c>
       <c r="B7" t="n">
-        <v>57893</v>
+        <v>57894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>129683182</v>
       </c>
       <c r="B8" t="n">
-        <v>57893</v>
+        <v>57894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129686779</v>
       </c>
       <c r="B9" t="n">
-        <v>57893</v>
+        <v>57894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49831-2025 artfynd.xlsx
+++ b/artfynd/A 49831-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129687266</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>57731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129687267</v>
       </c>
       <c r="B3" t="n">
-        <v>57894</v>
+        <v>57893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129685099</v>
       </c>
       <c r="B4" t="n">
-        <v>57894</v>
+        <v>57893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129685320</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129685100</v>
       </c>
       <c r="B6" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129685322</v>
       </c>
       <c r="B7" t="n">
-        <v>57894</v>
+        <v>57893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>129683182</v>
       </c>
       <c r="B8" t="n">
-        <v>57894</v>
+        <v>57893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129686779</v>
       </c>
       <c r="B9" t="n">
-        <v>57894</v>
+        <v>57893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49831-2025 artfynd.xlsx
+++ b/artfynd/A 49831-2025 artfynd.xlsx
@@ -1020,27 +1020,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129685320</v>
+        <v>129685100</v>
       </c>
       <c r="B5" t="n">
-        <v>57734</v>
+        <v>58108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459041</v>
+        <v>459097</v>
       </c>
       <c r="R5" t="n">
         <v>6229261</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,27 +1135,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129685100</v>
+        <v>129685320</v>
       </c>
       <c r="B6" t="n">
-        <v>58108</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1178,13 +1178,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459097</v>
+        <v>459041</v>
       </c>
       <c r="R6" t="n">
         <v>6229261</v>
       </c>
       <c r="S6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49831-2025 artfynd.xlsx
+++ b/artfynd/A 49831-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129687266</v>
       </c>
       <c r="B2" t="n">
-        <v>57731</v>
+        <v>57734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129687267</v>
       </c>
       <c r="B3" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129685099</v>
       </c>
       <c r="B4" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,27 +1020,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129685100</v>
+        <v>129685320</v>
       </c>
       <c r="B5" t="n">
-        <v>58108</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459097</v>
+        <v>459041</v>
       </c>
       <c r="R5" t="n">
         <v>6229261</v>
       </c>
       <c r="S5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,27 +1135,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129685320</v>
+        <v>129685100</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>58111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1178,13 +1178,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459041</v>
+        <v>459097</v>
       </c>
       <c r="R6" t="n">
         <v>6229261</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,7 +1253,7 @@
         <v>129685322</v>
       </c>
       <c r="B7" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>129683182</v>
       </c>
       <c r="B8" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129686779</v>
       </c>
       <c r="B9" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49831-2025 artfynd.xlsx
+++ b/artfynd/A 49831-2025 artfynd.xlsx
@@ -1020,27 +1020,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129685320</v>
+        <v>129685100</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>58111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459041</v>
+        <v>459097</v>
       </c>
       <c r="R5" t="n">
         <v>6229261</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,27 +1135,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129685100</v>
+        <v>129685320</v>
       </c>
       <c r="B6" t="n">
-        <v>58111</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1178,13 +1178,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459097</v>
+        <v>459041</v>
       </c>
       <c r="R6" t="n">
         <v>6229261</v>
       </c>
       <c r="S6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49831-2025 artfynd.xlsx
+++ b/artfynd/A 49831-2025 artfynd.xlsx
@@ -1020,27 +1020,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129685100</v>
+        <v>129685320</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459097</v>
+        <v>459041</v>
       </c>
       <c r="R5" t="n">
         <v>6229261</v>
       </c>
       <c r="S5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,27 +1135,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129685320</v>
+        <v>129685100</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>58111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1178,13 +1178,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459041</v>
+        <v>459097</v>
       </c>
       <c r="R6" t="n">
         <v>6229261</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49831-2025 artfynd.xlsx
+++ b/artfynd/A 49831-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>129687267</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>57897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129685099</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>57897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>129685100</v>
       </c>
       <c r="B6" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>129685322</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>57897</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>129683182</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>57897</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129686779</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>57897</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49831-2025 artfynd.xlsx
+++ b/artfynd/A 49831-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129687266</v>
+        <v>129685320</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458993</v>
+        <v>459041</v>
       </c>
       <c r="R2" t="n">
-        <v>6229582</v>
+        <v>6229261</v>
       </c>
       <c r="S2" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,37 +790,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129687267</v>
+        <v>129687266</v>
       </c>
       <c r="B3" t="n">
-        <v>57897</v>
+        <v>57947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -905,27 +905,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129685099</v>
+        <v>129685100</v>
       </c>
       <c r="B4" t="n">
-        <v>57897</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129685320</v>
+        <v>129683182</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1059,17 +1059,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Wulffahuset, Sk</t>
+          <t>Norra Kopparetorp, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459041</v>
+        <v>459168</v>
       </c>
       <c r="R5" t="n">
-        <v>6229261</v>
+        <v>6228763</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,27 +1135,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129685100</v>
+        <v>129685099</v>
       </c>
       <c r="B6" t="n">
         <v>58112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1253,7 +1253,7 @@
         <v>129685322</v>
       </c>
       <c r="B7" t="n">
-        <v>57897</v>
+        <v>58112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129683182</v>
+        <v>129686779</v>
       </c>
       <c r="B8" t="n">
-        <v>57897</v>
+        <v>58112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1404,17 +1404,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norra Kopparetorp, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459168</v>
+        <v>458910</v>
       </c>
       <c r="R8" t="n">
-        <v>6228763</v>
+        <v>6229889</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129686779</v>
+        <v>129687267</v>
       </c>
       <c r="B9" t="n">
-        <v>57897</v>
+        <v>58112</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1519,17 +1519,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Wulffahuset, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458910</v>
+        <v>458993</v>
       </c>
       <c r="R9" t="n">
-        <v>6229889</v>
+        <v>6229582</v>
       </c>
       <c r="S9" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49831-2025 artfynd.xlsx
+++ b/artfynd/A 49831-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129687266</v>
+        <v>134640341</v>
       </c>
       <c r="B3" t="n">
-        <v>57947</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -823,23 +823,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Wulffahuset, Sk</t>
+          <t>Wulffahuset, Lerjevallen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458993</v>
+        <v>458997</v>
       </c>
       <c r="R3" t="n">
-        <v>6229582</v>
+        <v>6229655</v>
       </c>
       <c r="S3" t="n">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,22 +864,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,22 +894,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Martin Kornhall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129685100</v>
+        <v>129687266</v>
       </c>
       <c r="B4" t="n">
-        <v>58327</v>
+        <v>57947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -948,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459097</v>
+        <v>458993</v>
       </c>
       <c r="R4" t="n">
-        <v>6229261</v>
+        <v>6229582</v>
       </c>
       <c r="S4" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,27 +1021,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129683182</v>
+        <v>129685100</v>
       </c>
       <c r="B5" t="n">
-        <v>58112</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1050,7 +1051,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1059,17 +1060,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norra Kopparetorp, Sk</t>
+          <t>Wulffahuset, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459168</v>
+        <v>459097</v>
       </c>
       <c r="R5" t="n">
-        <v>6228763</v>
+        <v>6229261</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1136,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129685099</v>
+        <v>129683182</v>
       </c>
       <c r="B6" t="n">
         <v>58112</v>
@@ -1165,7 +1166,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1174,17 +1175,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Wulffahuset, Sk</t>
+          <t>Norra Kopparetorp, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459097</v>
+        <v>459168</v>
       </c>
       <c r="R6" t="n">
-        <v>6229261</v>
+        <v>6228763</v>
       </c>
       <c r="S6" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,7 +1251,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129685322</v>
+        <v>129685099</v>
       </c>
       <c r="B7" t="n">
         <v>58112</v>
@@ -1280,7 +1281,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1293,13 +1294,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459041</v>
+        <v>459097</v>
       </c>
       <c r="R7" t="n">
         <v>6229261</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,7 +1366,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129686779</v>
+        <v>129685322</v>
       </c>
       <c r="B8" t="n">
         <v>58112</v>
@@ -1395,7 +1396,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1404,17 +1405,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Wulffahuset, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458910</v>
+        <v>459041</v>
       </c>
       <c r="R8" t="n">
-        <v>6229889</v>
+        <v>6229261</v>
       </c>
       <c r="S8" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1453,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,7 +1481,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129687267</v>
+        <v>129686779</v>
       </c>
       <c r="B9" t="n">
         <v>58112</v>
@@ -1510,7 +1511,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1519,17 +1520,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Wulffahuset, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458993</v>
+        <v>458910</v>
       </c>
       <c r="R9" t="n">
-        <v>6229582</v>
+        <v>6229889</v>
       </c>
       <c r="S9" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,6 +1593,237 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129687267</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Wulffahuset, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>458993</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6229582</v>
+      </c>
+      <c r="S10" t="n">
+        <v>73</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134640515</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Wulffahuset, Wulffahuset, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>458997</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6229655</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vånga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Martin Kornhall</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49831-2025 artfynd.xlsx
+++ b/artfynd/A 49831-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129685320</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134640341</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129687266</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129685100</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1248,6 +1273,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129683182</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1363,6 +1393,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129685099</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1478,6 +1513,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129685322</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1593,6 +1633,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129686779</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1708,6 +1753,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129687267</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1824,8 +1874,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134640515</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>